--- a/tests/v1/fixtures/office6m/2026-10/bank_statements/TCB_HOLD_USD_2026-09.xlsx
+++ b/tests/v1/fixtures/office6m/2026-10/bank_statements/TCB_HOLD_USD_2026-09.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -476,31 +476,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BF-TCB-HOLD-USD-09</t>
+          <t>ACH-55201</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bank_fee</t>
+          <t>card_debit</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Account maintenance fee</t>
+          <t>ACH DEBIT MERCHANT 55201 SINGAPORE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tidewater Commercial Bank (synthetic)</t>
+          <t>Unknown merchant</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-46.51</v>
+        <v>-3980</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -511,33 +511,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BF-TCB-HOLD-USD-09</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bank_fee</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Account maintenance fee</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Tidewater Commercial Bank (synthetic)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-46.51</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>IN-TCB-HOLD-USD-09</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>interest</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Credit interest</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Tidewater Commercial Bank (synthetic)</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>318.98</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -614,13 +649,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>198829.25</v>
+        <v>202809.25</v>
       </c>
       <c r="E2" t="n">
         <v>787.02</v>
       </c>
       <c r="F2" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="3">
@@ -640,13 +675,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="4">
@@ -666,13 +701,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="5">
@@ -692,13 +727,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="6">
@@ -718,13 +753,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="7">
@@ -744,13 +779,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="8">
@@ -770,13 +805,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="9">
@@ -796,13 +831,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="10">
@@ -822,13 +857,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="11">
@@ -848,13 +883,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="12">
@@ -874,13 +909,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="13">
@@ -900,13 +935,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="14">
@@ -926,13 +961,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="15">
@@ -952,13 +987,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="16">
@@ -978,13 +1013,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="17">
@@ -1004,13 +1039,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
     <row r="18">
@@ -1030,10 +1065,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-3980</v>
       </c>
       <c r="F18" t="n">
         <v>199616.27</v>
